--- a/Backtest/11-01-21/S&P500stock_11-01-21period252RS90.xlsx
+++ b/Backtest/11-01-21/S&P500stock_11-01-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
   <si>
     <t>Stock</t>
   </si>
@@ -127,130 +127,193 @@
     <t>EM Rating</t>
   </si>
   <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>MOS</t>
+  </si>
+  <si>
     <t>TSLA</t>
   </si>
   <si>
-    <t>POOL</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>RVTY</t>
-  </si>
-  <si>
-    <t>ALGN</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>TSCO</t>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>WFC</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>HES</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>OXY</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>BAC</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>OKE</t>
+  </si>
+  <si>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>CBRE</t>
+  </si>
+  <si>
+    <t>EPAM</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>MV</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-02-17</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
+    <t>2021-11-04</t>
+  </si>
+  <si>
+    <t>2022-02-22</t>
+  </si>
+  <si>
+    <t>2022-01-26</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2022-01-27</t>
+  </si>
+  <si>
+    <t>2022-02-03</t>
+  </si>
+  <si>
+    <t>2022-01-14</t>
+  </si>
+  <si>
+    <t>2022-01-24</t>
+  </si>
+  <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
+    <t>2022-01-21</t>
+  </si>
+  <si>
+    <t>2022-01-18</t>
+  </si>
+  <si>
+    <t>2022-01-19</t>
+  </si>
+  <si>
+    <t>2021-11-18</t>
+  </si>
+  <si>
+    <t>2022-02-24</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
   </si>
   <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Agricultural Inputs</t>
   </si>
   <si>
     <t>Auto Manufacturers</t>
   </si>
   <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Banks - Diversified</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Specialty Chemicals</t>
   </si>
   <si>
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Credit Services</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Software - Application</t>
-  </si>
-  <si>
-    <t>Specialty Retail</t>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Real Estate Services</t>
   </si>
 </sst>
 </file>
@@ -608,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -729,46 +792,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>98.18181818181819</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="D2">
-        <v>293.34</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="E2">
-        <v>3.65</v>
+        <v>1.91</v>
       </c>
       <c r="F2">
-        <v>1.972885018801462</v>
+        <v>-0.0181689082723466</v>
       </c>
       <c r="G2">
-        <v>3.77</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
-        <v>1.173626489489408</v>
+        <v>0.3439705474188656</v>
       </c>
       <c r="I2">
-        <v>261.1279998779297</v>
+        <v>93.66999969482421</v>
       </c>
       <c r="J2">
-        <v>228.8134994506836</v>
+        <v>90.55450057983398</v>
       </c>
       <c r="K2">
-        <v>189.9204656982422</v>
+        <v>79.42279983520508</v>
       </c>
       <c r="L2">
-        <v>116.6486597061157</v>
+        <v>74.57089994430542</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>1.37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>14</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -777,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>5.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -792,49 +852,49 @@
         <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>23.37</v>
+        <v>33.02</v>
       </c>
       <c r="Y2">
-        <v>294.83</v>
+        <v>95.64</v>
       </c>
       <c r="Z2">
-        <v>474.06</v>
+        <v>48.73</v>
       </c>
       <c r="AA2">
-        <v>-14.64</v>
+        <v>-0.68</v>
       </c>
       <c r="AB2">
-        <v>173.82</v>
+        <v>500</v>
       </c>
       <c r="AC2">
-        <v>125.58</v>
+        <v>2328.57</v>
       </c>
       <c r="AD2">
-        <v>2.18</v>
+        <v>4.34</v>
       </c>
       <c r="AE2">
-        <v>190.74</v>
+        <v>33.33</v>
       </c>
       <c r="AF2">
-        <v>447.76</v>
+        <v>101.72</v>
       </c>
       <c r="AG2">
-        <v>-85.84</v>
+        <v>928.5700000000001</v>
       </c>
       <c r="AH2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AI2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="AK2">
-        <v>61.34048342829396</v>
+        <v>83.49109265102875</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -842,49 +902,49 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>95.76612903225806</v>
+        <v>95.35353535353536</v>
       </c>
       <c r="C3">
-        <v>480</v>
+        <v>149</v>
       </c>
       <c r="D3">
-        <v>390.99</v>
+        <v>41.57</v>
       </c>
       <c r="E3">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="F3">
-        <v>-0.1909772369674873</v>
+        <v>-0.6984128339889742</v>
       </c>
       <c r="G3">
-        <v>2.98</v>
+        <v>2.28</v>
       </c>
       <c r="H3">
-        <v>0.2928491683716444</v>
+        <v>0.1786612270327193</v>
       </c>
       <c r="I3">
-        <v>372.2160034179688</v>
+        <v>41.77999954223633</v>
       </c>
       <c r="J3">
-        <v>361.3835021972656</v>
+        <v>41.0644998550415</v>
       </c>
       <c r="K3">
-        <v>351.2894006347656</v>
+        <v>36.33940013885498</v>
       </c>
       <c r="L3">
-        <v>296.6280003356933</v>
+        <v>33.00490014076233</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -893,58 +953,58 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>2.222222222222222</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>160.35</v>
+        <v>16.01</v>
       </c>
       <c r="Y3">
-        <v>401.29</v>
+        <v>43.24</v>
       </c>
       <c r="Z3">
-        <v>13.66</v>
+        <v>12.23</v>
       </c>
       <c r="AA3">
-        <v>18.81</v>
+        <v>25.51</v>
       </c>
       <c r="AB3">
-        <v>15.98</v>
+        <v>226.44</v>
       </c>
       <c r="AC3">
-        <v>560</v>
+        <v>5850</v>
       </c>
       <c r="AD3">
-        <v>20.2</v>
+        <v>4.17</v>
       </c>
       <c r="AE3">
-        <v>-24.62</v>
+        <v>180.49</v>
       </c>
       <c r="AF3">
-        <v>411.69</v>
+        <v>-81.28</v>
       </c>
       <c r="AG3">
-        <v>71.11</v>
+        <v>11050</v>
       </c>
       <c r="AH3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="AI3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="AK3">
-        <v>53.25330614236726</v>
+        <v>80.11618507400328</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -952,58 +1012,61 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.17741935483872</v>
+        <v>97.77777777777777</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>94.58</v>
+        <v>371.33</v>
       </c>
       <c r="E4">
-        <v>1.97</v>
+        <v>2.93</v>
       </c>
       <c r="F4">
-        <v>-0.09261986170526228</v>
+        <v>1.909188881258099</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="H4">
-        <v>-0.2869029923640984</v>
+        <v>0.3605014794574806</v>
       </c>
       <c r="I4">
-        <v>93.02800140380859</v>
+        <v>351.4793334960938</v>
       </c>
       <c r="J4">
-        <v>93.29650077819824</v>
+        <v>294.5018341064453</v>
       </c>
       <c r="K4">
-        <v>88.18200012207031</v>
+        <v>266.4286016845703</v>
       </c>
       <c r="L4">
-        <v>71.33860006332398</v>
+        <v>238.8869340515137</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="N4">
-        <v>1.05</v>
+        <v>1.32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -1015,46 +1078,46 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>36.75</v>
+        <v>126.37</v>
       </c>
       <c r="Y4">
-        <v>97.98</v>
+        <v>371.74</v>
       </c>
       <c r="Z4">
-        <v>99.62</v>
+        <v>870.86</v>
       </c>
       <c r="AA4">
-        <v>-8.85</v>
+        <v>-104.17</v>
       </c>
       <c r="AB4">
-        <v>116.97</v>
+        <v>298.99</v>
       </c>
       <c r="AC4">
-        <v>105.88</v>
+        <v>440</v>
       </c>
       <c r="AD4">
-        <v>10.09</v>
+        <v>5.95</v>
       </c>
       <c r="AE4">
-        <v>153.38</v>
+        <v>37.3</v>
       </c>
       <c r="AF4">
-        <v>-7.14</v>
+        <v>156.56</v>
       </c>
       <c r="AG4">
-        <v>-12.5</v>
+        <v>53.3</v>
       </c>
       <c r="AH4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="AI4" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AK4">
-        <v>52.51618062292123</v>
+        <v>79.81849240066228</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1062,46 +1125,46 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>90.5241935483871</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="C5">
-        <v>370</v>
+        <v>92</v>
       </c>
       <c r="D5">
-        <v>159.76</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E5">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="F5">
-        <v>-0.4245760032152716</v>
+        <v>-1.208595778276445</v>
       </c>
       <c r="G5">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="H5">
-        <v>-0.6548226328310123</v>
+        <v>-0.6478853748980111</v>
       </c>
       <c r="I5">
-        <v>154.8139953613281</v>
+        <v>67.08399963378906</v>
       </c>
       <c r="J5">
-        <v>145.3810005187988</v>
+        <v>65.81200008392334</v>
       </c>
       <c r="K5">
-        <v>138.1656001281738</v>
+        <v>61.78180015563965</v>
       </c>
       <c r="L5">
-        <v>113.5600501251221</v>
+        <v>57.21169990539551</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1113,58 +1176,58 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>62.91</v>
+        <v>28.16</v>
       </c>
       <c r="Y5">
-        <v>162.4</v>
+        <v>68.78</v>
       </c>
       <c r="Z5">
-        <v>14.09</v>
+        <v>39.51</v>
       </c>
       <c r="AA5">
-        <v>15.86</v>
+        <v>15.3</v>
       </c>
       <c r="AB5">
-        <v>37.04</v>
+        <v>189.22</v>
       </c>
       <c r="AC5">
-        <v>167.8</v>
+        <v>1062.5</v>
       </c>
       <c r="AD5">
-        <v>5.47</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>28.46</v>
+        <v>3637.84</v>
       </c>
       <c r="AF5">
-        <v>310</v>
+        <v>-178.72</v>
       </c>
       <c r="AG5">
-        <v>-49.15</v>
+        <v>134.56</v>
       </c>
       <c r="AH5" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AI5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AJ5" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AK5">
-        <v>47.42857038560203</v>
+        <v>69.64268941744419</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1172,49 +1235,49 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>96.9758064516129</v>
+        <v>98.58585858585859</v>
       </c>
       <c r="C6">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D6">
-        <v>570.53</v>
+        <v>331.91</v>
       </c>
       <c r="E6">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="F6">
-        <v>-0.6212907537397213</v>
+        <v>-1.151908784466726</v>
       </c>
       <c r="G6">
-        <v>4.95</v>
+        <v>1.39</v>
       </c>
       <c r="H6">
-        <v>2.489217931158978</v>
+        <v>-1.292591724403981</v>
       </c>
       <c r="I6">
-        <v>547.8780151367188</v>
+        <v>325.8480041503906</v>
       </c>
       <c r="J6">
-        <v>528.4395065307617</v>
+        <v>314.2639999389648</v>
       </c>
       <c r="K6">
-        <v>495.2926043701172</v>
+        <v>312.0217987060547</v>
       </c>
       <c r="L6">
-        <v>329.812950592041</v>
+        <v>240.2688499450684</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1223,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1235,46 +1298,46 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>127.88</v>
+        <v>117.13</v>
       </c>
       <c r="Y6">
-        <v>579.5</v>
+        <v>332.3</v>
       </c>
       <c r="Z6">
-        <v>25.91</v>
+        <v>20.97</v>
       </c>
       <c r="AA6">
-        <v>83.59</v>
+        <v>17.97</v>
       </c>
       <c r="AB6">
-        <v>225.63</v>
+        <v>128.22</v>
       </c>
       <c r="AC6">
-        <v>14.94</v>
+        <v>1563.16</v>
       </c>
       <c r="AD6">
-        <v>4.59</v>
+        <v>51.41</v>
       </c>
       <c r="AE6">
-        <v>440.38</v>
+        <v>69.89</v>
       </c>
       <c r="AF6">
-        <v>-102.69</v>
+        <v>38.81</v>
       </c>
       <c r="AG6">
-        <v>1154.55</v>
+        <v>605.26</v>
       </c>
       <c r="AH6" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AI6" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="AK6">
-        <v>39.55254286079886</v>
+        <v>68.40052320249256</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1282,58 +1345,61 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>97.37903225806451</v>
+        <v>97.97979797979798</v>
       </c>
       <c r="C7">
-        <v>330</v>
+        <v>164</v>
       </c>
       <c r="D7">
-        <v>132.15</v>
+        <v>138.42</v>
       </c>
       <c r="E7">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="F7">
-        <v>-0.3262186279530465</v>
+        <v>0.5298053652216042</v>
       </c>
       <c r="G7">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="H7">
-        <v>-0.6659717128451609</v>
+        <v>-0.2015502098554168</v>
       </c>
       <c r="I7">
-        <v>125.0300003051758</v>
+        <v>139.202001953125</v>
       </c>
       <c r="J7">
-        <v>120.1540000915527</v>
+        <v>125.5510009765625</v>
       </c>
       <c r="K7">
-        <v>110.5680000305176</v>
+        <v>125.1488006591797</v>
       </c>
       <c r="L7">
-        <v>85.17969989776611</v>
+        <v>96.46745040893555</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
-        <v>1.13</v>
+        <v>1.11</v>
+      </c>
+      <c r="O7" t="s">
+        <v>63</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>14.44444444444444</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1345,46 +1411,46 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>42.87</v>
+        <v>49.41</v>
       </c>
       <c r="Y7">
-        <v>133.48</v>
+        <v>143.03</v>
       </c>
       <c r="Z7">
-        <v>14.65</v>
+        <v>84.05</v>
       </c>
       <c r="AA7">
-        <v>404.54</v>
+        <v>40.78</v>
       </c>
       <c r="AB7">
-        <v>21.59</v>
+        <v>231.53</v>
       </c>
       <c r="AC7">
-        <v>81.08</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AD7">
-        <v>11.17</v>
+        <v>15.41</v>
       </c>
       <c r="AE7">
-        <v>17.54</v>
+        <v>6.59</v>
       </c>
       <c r="AF7">
-        <v>7.55</v>
+        <v>-26.32</v>
       </c>
       <c r="AG7">
-        <v>43.24</v>
+        <v>118.58</v>
       </c>
       <c r="AH7" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="AI7" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ7" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="AK7">
-        <v>35.38987516584783</v>
+        <v>67.70289122747116</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1392,43 +1458,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>94.55645161290323</v>
+        <v>93.13131313131314</v>
       </c>
       <c r="C8">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>156.64</v>
+        <v>17.08</v>
       </c>
       <c r="E8">
-        <v>2.18</v>
+        <v>2.82</v>
       </c>
       <c r="F8">
-        <v>0.1655682483580785</v>
+        <v>1.701336570622463</v>
       </c>
       <c r="G8">
-        <v>2.61</v>
+        <v>2.28</v>
       </c>
       <c r="H8">
-        <v>-0.119666792151865</v>
+        <v>0.1786612270327193</v>
       </c>
       <c r="I8">
-        <v>152.8919982910156</v>
+        <v>16.27800006866455</v>
       </c>
       <c r="J8">
-        <v>149.6619995117188</v>
+        <v>15.57000012397766</v>
       </c>
       <c r="K8">
-        <v>145.9374002075195</v>
+        <v>14.18180002212524</v>
       </c>
       <c r="L8">
-        <v>109.1944499206543</v>
+        <v>13.24244997501373</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1455,46 +1521,46 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>58</v>
+        <v>7.61</v>
       </c>
       <c r="Y8">
-        <v>161.07</v>
+        <v>17.58</v>
       </c>
       <c r="Z8">
-        <v>135.21</v>
+        <v>57.15</v>
       </c>
       <c r="AA8">
-        <v>5.05</v>
+        <v>5.35</v>
       </c>
       <c r="AB8">
-        <v>3.15</v>
+        <v>196</v>
       </c>
       <c r="AC8">
-        <v>222.22</v>
+        <v>165.71</v>
       </c>
       <c r="AD8">
-        <v>48.71</v>
+        <v>4.96</v>
       </c>
       <c r="AE8">
-        <v>248</v>
+        <v>228.57</v>
       </c>
       <c r="AF8">
-        <v>82.93000000000001</v>
+        <v>-82.93000000000001</v>
       </c>
       <c r="AG8">
-        <v>-49.38</v>
+        <v>217.14</v>
       </c>
       <c r="AH8" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="AI8" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="AJ8" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AK8">
-        <v>30.32748182503727</v>
+        <v>60.59621211647715</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1502,43 +1568,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>97.98387096774194</v>
+        <v>97.17171717171718</v>
       </c>
       <c r="C9">
-        <v>463</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>387.41</v>
+        <v>51.16</v>
       </c>
       <c r="E9">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="F9">
-        <v>0.2024522640814126</v>
+        <v>0.03851808553737244</v>
       </c>
       <c r="G9">
-        <v>3.01</v>
+        <v>2.02</v>
       </c>
       <c r="H9">
-        <v>0.3262964084140909</v>
+        <v>-0.2511430059712603</v>
       </c>
       <c r="I9">
-        <v>372.5280029296875</v>
+        <v>50.76399993896484</v>
       </c>
       <c r="J9">
-        <v>350.0215026855469</v>
+        <v>48.85100002288819</v>
       </c>
       <c r="K9">
-        <v>330.7852020263672</v>
+        <v>47.42559997558594</v>
       </c>
       <c r="L9">
-        <v>262.2404006958008</v>
+        <v>43.31815011978149</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1547,64 +1613,64 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>130.12</v>
+        <v>20.84</v>
       </c>
       <c r="Y9">
-        <v>392.74</v>
+        <v>51.64</v>
       </c>
       <c r="Z9">
-        <v>13.13</v>
+        <v>189.84</v>
       </c>
       <c r="AA9">
-        <v>55.17</v>
+        <v>3.4</v>
       </c>
       <c r="AB9">
-        <v>9.15</v>
+        <v>293.64</v>
       </c>
       <c r="AC9">
-        <v>65.33</v>
+        <v>61.64</v>
       </c>
       <c r="AD9">
-        <v>6.08</v>
+        <v>3.16</v>
       </c>
       <c r="AE9">
-        <v>85.06999999999999</v>
+        <v>-15.11</v>
       </c>
       <c r="AF9">
-        <v>-16.25</v>
+        <v>34.95</v>
       </c>
       <c r="AG9">
-        <v>6.67</v>
+        <v>41.1</v>
       </c>
       <c r="AH9" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="AI9" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="AK9">
-        <v>28.11430859660445</v>
+        <v>59.73148175677394</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1612,46 +1678,46 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>94.75806451612904</v>
+        <v>95.75757575757575</v>
       </c>
       <c r="C10">
-        <v>422</v>
+        <v>134</v>
       </c>
       <c r="D10">
-        <v>262.8</v>
+        <v>79.67</v>
       </c>
       <c r="E10">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="F10">
-        <v>-0.5598173942008308</v>
+        <v>-0.5094561879565779</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="H10">
-        <v>-0.77746251298665</v>
+        <v>-0.697478171013855</v>
       </c>
       <c r="I10">
-        <v>256.9859985351562</v>
+        <v>77.33399963378906</v>
       </c>
       <c r="J10">
-        <v>251.9939994812012</v>
+        <v>69.09800014495849</v>
       </c>
       <c r="K10">
-        <v>236.2387997436524</v>
+        <v>65.705599899292</v>
       </c>
       <c r="L10">
-        <v>199.916499786377</v>
+        <v>56.63249996185303</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>2</v>
@@ -1663,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.777777777777778</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -1675,46 +1741,46 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>104.9</v>
+        <v>33.65</v>
       </c>
       <c r="Y10">
-        <v>264.33</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Z10">
-        <v>33.3</v>
+        <v>37.34</v>
       </c>
       <c r="AA10">
-        <v>25.71</v>
+        <v>-19100</v>
       </c>
       <c r="AB10">
-        <v>3.77</v>
+        <v>340.09</v>
       </c>
       <c r="AC10">
-        <v>89.86</v>
+        <v>17.74</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>8.34</v>
       </c>
       <c r="AE10">
-        <v>-21.56</v>
+        <v>-23.16</v>
       </c>
       <c r="AF10">
-        <v>128.77</v>
+        <v>7.55</v>
       </c>
       <c r="AG10">
-        <v>5.8</v>
+        <v>42.47</v>
       </c>
       <c r="AH10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="AI10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AK10">
-        <v>24.56873174614586</v>
+        <v>56.58123680250154</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1722,46 +1788,46 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>97.78225806451613</v>
+        <v>99.79797979797979</v>
       </c>
       <c r="C11">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D11">
-        <v>242.46</v>
+        <v>40.08</v>
       </c>
       <c r="E11">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="F11">
-        <v>-0.01885183025859377</v>
+        <v>1.058883974112314</v>
       </c>
       <c r="G11">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="H11">
-        <v>0.1479111281877088</v>
+        <v>1.401950197890201</v>
       </c>
       <c r="I11">
-        <v>234.2320007324219</v>
+        <v>40.47200012207031</v>
       </c>
       <c r="J11">
-        <v>231.8434989929199</v>
+        <v>39.87900009155273</v>
       </c>
       <c r="K11">
-        <v>212.588798828125</v>
+        <v>34.12900009155273</v>
       </c>
       <c r="L11">
-        <v>177.8942748641968</v>
+        <v>26.83745003700257</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -1773,58 +1839,58 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>82.06999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="Y11">
-        <v>244.25</v>
+        <v>41.98</v>
       </c>
       <c r="Z11">
-        <v>234.47</v>
+        <v>19.82</v>
       </c>
       <c r="AA11">
-        <v>35.3</v>
+        <v>-0.01</v>
       </c>
       <c r="AB11">
-        <v>3.09</v>
+        <v>102.32</v>
       </c>
       <c r="AC11">
-        <v>102.33</v>
+        <v>252</v>
       </c>
       <c r="AD11">
-        <v>5.51</v>
+        <v>3.06</v>
       </c>
       <c r="AE11">
-        <v>-33.08</v>
+        <v>15.15</v>
       </c>
       <c r="AF11">
-        <v>1757.14</v>
+        <v>222.22</v>
       </c>
       <c r="AG11">
-        <v>-83.72</v>
+        <v>-8</v>
       </c>
       <c r="AH11" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AI11" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AK11">
-        <v>22.99922568202899</v>
+        <v>56.13585488082424</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1832,52 +1898,49 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>97.58064516129032</v>
+        <v>94.54545454545455</v>
       </c>
       <c r="C12">
-        <v>459</v>
+        <v>238</v>
       </c>
       <c r="D12">
-        <v>307.53</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="E12">
-        <v>1.27</v>
+        <v>2.23</v>
       </c>
       <c r="F12">
-        <v>-0.9532468952497306</v>
+        <v>0.5864923590313228</v>
       </c>
       <c r="G12">
-        <v>1.77</v>
+        <v>2.59</v>
       </c>
       <c r="H12">
-        <v>-1.056189513340372</v>
+        <v>0.6911201202297724</v>
       </c>
       <c r="I12">
-        <v>296.4640014648438</v>
+        <v>85.71199951171874</v>
       </c>
       <c r="J12">
-        <v>280.3220001220703</v>
+        <v>87.26399993896484</v>
       </c>
       <c r="K12">
-        <v>279.4818011474609</v>
+        <v>77.63399993896485</v>
       </c>
       <c r="L12">
-        <v>246.7426999664307</v>
+        <v>74.92670007705688</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="N12">
-        <v>1.06</v>
-      </c>
-      <c r="O12" t="s">
-        <v>52</v>
+        <v>1.1</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1886,58 +1949,58 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>124.53</v>
+        <v>35.91</v>
       </c>
       <c r="Y12">
-        <v>312.12</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="Z12">
-        <v>20.84</v>
+        <v>24.21</v>
       </c>
       <c r="AA12">
-        <v>26.94</v>
+        <v>-0.02</v>
       </c>
       <c r="AB12">
-        <v>6.3</v>
+        <v>105.97</v>
       </c>
       <c r="AC12">
-        <v>29.07</v>
+        <v>223.33</v>
       </c>
       <c r="AD12">
-        <v>4.79</v>
+        <v>2.96</v>
       </c>
       <c r="AE12">
-        <v>-10.48</v>
+        <v>254.17</v>
       </c>
       <c r="AF12">
-        <v>22.77</v>
+        <v>-129.27</v>
       </c>
       <c r="AG12">
-        <v>17.44</v>
+        <v>373.33</v>
       </c>
       <c r="AH12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AI12" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AJ12" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="AK12">
-        <v>17.81120849356769</v>
+        <v>55.87934850968824</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1945,46 +2008,46 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>93.14516129032258</v>
+        <v>92.72727272727272</v>
       </c>
       <c r="C13">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D13">
-        <v>50.16</v>
+        <v>24.99</v>
       </c>
       <c r="E13">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="F13">
-        <v>-0.375397315584159</v>
+        <v>0.8132403342701989</v>
       </c>
       <c r="G13">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="H13">
-        <v>-0.6213753927885652</v>
+        <v>0.6580582561525432</v>
       </c>
       <c r="I13">
-        <v>49.70299911499023</v>
+        <v>25.62000007629394</v>
       </c>
       <c r="J13">
-        <v>48.66204986572266</v>
+        <v>24.95599994659424</v>
       </c>
       <c r="K13">
-        <v>45.27928016662597</v>
+        <v>22.18099990844727</v>
       </c>
       <c r="L13">
-        <v>34.81789490699768</v>
+        <v>21.61070003509521</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -1996,58 +2059,58 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>18.14</v>
+        <v>11.48</v>
       </c>
       <c r="Y13">
-        <v>52.22</v>
+        <v>26.75</v>
       </c>
       <c r="Z13">
-        <v>48.85</v>
+        <v>19.33</v>
       </c>
       <c r="AA13">
-        <v>86</v>
+        <v>-0.2</v>
       </c>
       <c r="AB13">
-        <v>1.52</v>
+        <v>108.8</v>
       </c>
       <c r="AC13">
-        <v>58.82</v>
+        <v>204</v>
       </c>
       <c r="AD13">
-        <v>15.18</v>
+        <v>4.22</v>
       </c>
       <c r="AE13">
-        <v>18.12</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>21.21</v>
+        <v>36.84</v>
       </c>
       <c r="AG13">
-        <v>10.92</v>
+        <v>176</v>
       </c>
       <c r="AH13" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AI13" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AK13">
-        <v>13.7396829365093</v>
+        <v>55.6882065459426</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2055,43 +2118,43 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>95.96774193548387</v>
+        <v>92.12121212121212</v>
       </c>
       <c r="C14">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="D14">
-        <v>104.1</v>
+        <v>56.8</v>
       </c>
       <c r="E14">
-        <v>4.19</v>
+        <v>1.51</v>
       </c>
       <c r="F14">
-        <v>2.636797301821481</v>
+        <v>-0.773995492401933</v>
       </c>
       <c r="G14">
-        <v>3.93</v>
+        <v>2.38</v>
       </c>
       <c r="H14">
-        <v>1.35201176971579</v>
+        <v>0.3439705474188656</v>
       </c>
       <c r="I14">
-        <v>100.5380004882812</v>
+        <v>57.75600051879883</v>
       </c>
       <c r="J14">
-        <v>96.7180004119873</v>
+        <v>59.80300025939941</v>
       </c>
       <c r="K14">
-        <v>90.81199981689453</v>
+        <v>53.10739997863769</v>
       </c>
       <c r="L14">
-        <v>66.28259996414185</v>
+        <v>49.50020015716553</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="N14">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2100,64 +2163,64 @@
         <v>0</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>3.888888888888888</v>
+        <v>5</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14">
-        <v>28.47</v>
+        <v>25.96</v>
       </c>
       <c r="Y14">
-        <v>109.62</v>
+        <v>63.4</v>
       </c>
       <c r="Z14">
-        <v>7.07</v>
+        <v>11.14</v>
       </c>
       <c r="AA14">
-        <v>0.7</v>
+        <v>89.06</v>
       </c>
       <c r="AB14">
-        <v>457.63</v>
+        <v>30.06</v>
       </c>
       <c r="AC14">
-        <v>360.71</v>
+        <v>976.92</v>
       </c>
       <c r="AD14">
-        <v>2.87</v>
+        <v>5.32</v>
       </c>
       <c r="AE14">
-        <v>317.14</v>
+        <v>62.86</v>
       </c>
       <c r="AF14">
-        <v>-59.3</v>
+        <v>70.73</v>
       </c>
       <c r="AG14">
-        <v>253.57</v>
+        <v>415.38</v>
       </c>
       <c r="AH14" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AK14">
-        <v>79.02860104782347</v>
+        <v>54.08124465484304</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2165,49 +2228,49 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>92.33870967741935</v>
+        <v>99.5959595959596</v>
       </c>
       <c r="C15">
-        <v>410</v>
+        <v>230</v>
       </c>
       <c r="D15">
-        <v>127.94</v>
+        <v>107.19</v>
       </c>
       <c r="E15">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="F15">
-        <v>-0.6581747694630558</v>
+        <v>0.09520507934709148</v>
       </c>
       <c r="G15">
-        <v>1.89</v>
+        <v>2.85</v>
       </c>
       <c r="H15">
-        <v>-0.9224005531705858</v>
+        <v>1.120924353233753</v>
       </c>
       <c r="I15">
-        <v>121.8160003662109</v>
+        <v>108.9760025024414</v>
       </c>
       <c r="J15">
-        <v>118.4705001831055</v>
+        <v>108.3595016479492</v>
       </c>
       <c r="K15">
-        <v>107.0080001831055</v>
+        <v>91.68900100708008</v>
       </c>
       <c r="L15">
-        <v>85.65155021667481</v>
+        <v>81.29860019683838</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2216,58 +2279,58 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>15</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>43.9</v>
+        <v>24.57</v>
       </c>
       <c r="Y15">
-        <v>129.26</v>
+        <v>114.73</v>
       </c>
       <c r="Z15">
-        <v>9.619999999999999</v>
+        <v>17.01</v>
       </c>
       <c r="AA15">
-        <v>565</v>
+        <v>2.68</v>
       </c>
       <c r="AB15">
-        <v>1312.5</v>
+        <v>64.73</v>
       </c>
       <c r="AC15">
-        <v>48.39</v>
+        <v>124.11</v>
       </c>
       <c r="AD15">
-        <v>3.71</v>
+        <v>2.76</v>
       </c>
       <c r="AE15">
-        <v>53.33</v>
+        <v>26.87</v>
       </c>
       <c r="AF15">
-        <v>400</v>
+        <v>128.63</v>
       </c>
       <c r="AG15">
-        <v>-80.65000000000001</v>
+        <v>33.62</v>
       </c>
       <c r="AH15" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AI15" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AJ15" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AK15">
-        <v>76.11578259277927</v>
+        <v>48.69392599217803</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2275,109 +2338,1322 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>91.93548387096774</v>
+        <v>94.94949494949495</v>
       </c>
       <c r="C16">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="D16">
-        <v>29.86</v>
+        <v>32.26</v>
       </c>
       <c r="E16">
+        <v>2.13</v>
+      </c>
+      <c r="F16">
+        <v>0.3975357129989259</v>
+      </c>
+      <c r="G16">
+        <v>2.4</v>
+      </c>
+      <c r="H16">
+        <v>0.3770324114960948</v>
+      </c>
+      <c r="I16">
+        <v>33.34399948120117</v>
+      </c>
+      <c r="J16">
+        <v>32.90399990081787</v>
+      </c>
+      <c r="K16">
+        <v>30.15279998779297</v>
+      </c>
+      <c r="L16">
+        <v>29.20879995346069</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>1.11</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>14.32</v>
+      </c>
+      <c r="Y16">
+        <v>36.87</v>
+      </c>
+      <c r="Z16">
+        <v>42.21</v>
+      </c>
+      <c r="AA16">
+        <v>-5.72</v>
+      </c>
+      <c r="AB16">
+        <v>116.23</v>
+      </c>
+      <c r="AC16">
+        <v>39.29</v>
+      </c>
+      <c r="AD16">
+        <v>4.11</v>
+      </c>
+      <c r="AE16">
+        <v>25.81</v>
+      </c>
+      <c r="AF16">
+        <v>47.62</v>
+      </c>
+      <c r="AG16">
+        <v>-25</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK16">
+        <v>48.0997420556477</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17">
+        <v>99.39393939393939</v>
+      </c>
+      <c r="C17">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>33.53</v>
+      </c>
+      <c r="E17">
+        <v>2.55</v>
+      </c>
+      <c r="F17">
+        <v>1.191153626334992</v>
+      </c>
+      <c r="G17">
+        <v>3.32</v>
+      </c>
+      <c r="H17">
+        <v>1.897878159048639</v>
+      </c>
+      <c r="I17">
+        <v>34.24800033569336</v>
+      </c>
+      <c r="J17">
+        <v>33.11099987030029</v>
+      </c>
+      <c r="K17">
+        <v>29.10199989318848</v>
+      </c>
+      <c r="L17">
+        <v>27.15590001106262</v>
+      </c>
+      <c r="M17">
+        <v>1.03</v>
+      </c>
+      <c r="N17">
+        <v>1.18</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>8.85</v>
+      </c>
+      <c r="Y17">
+        <v>35.75</v>
+      </c>
+      <c r="Z17">
+        <v>29.21</v>
+      </c>
+      <c r="AA17">
+        <v>1.06</v>
+      </c>
+      <c r="AB17">
+        <v>68.14</v>
+      </c>
+      <c r="AC17">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="AD17">
+        <v>1.18</v>
+      </c>
+      <c r="AE17">
+        <v>72.97</v>
+      </c>
+      <c r="AF17">
+        <v>73.19</v>
+      </c>
+      <c r="AG17">
+        <v>66.09</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK17">
+        <v>47.25719250288537</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18">
+        <v>93.73737373737374</v>
+      </c>
+      <c r="C18">
+        <v>254</v>
+      </c>
+      <c r="D18">
+        <v>413.35</v>
+      </c>
+      <c r="E18">
+        <v>1.47</v>
+      </c>
+      <c r="F18">
+        <v>-0.8495781508148917</v>
+      </c>
+      <c r="G18">
+        <v>1.48</v>
+      </c>
+      <c r="H18">
+        <v>-1.14381333605645</v>
+      </c>
+      <c r="I18">
+        <v>414.3039978027344</v>
+      </c>
+      <c r="J18">
+        <v>400.6979995727539</v>
+      </c>
+      <c r="K18">
+        <v>400.2488006591797</v>
+      </c>
+      <c r="L18">
+        <v>361.5598501586914</v>
+      </c>
+      <c r="M18">
+        <v>1.03</v>
+      </c>
+      <c r="N18">
+        <v>1.04</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>185.52</v>
+      </c>
+      <c r="Y18">
+        <v>420.76</v>
+      </c>
+      <c r="Z18">
+        <v>133.78</v>
+      </c>
+      <c r="AA18">
+        <v>3.84</v>
+      </c>
+      <c r="AB18">
+        <v>106.67</v>
+      </c>
+      <c r="AC18">
+        <v>23.9</v>
+      </c>
+      <c r="AD18">
+        <v>5.58</v>
+      </c>
+      <c r="AE18">
+        <v>-0.53</v>
+      </c>
+      <c r="AF18">
+        <v>-19.04</v>
+      </c>
+      <c r="AG18">
+        <v>53.85</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK18">
+        <v>44.79077662713916</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19">
+        <v>97.57575757575758</v>
+      </c>
+      <c r="C19">
+        <v>248</v>
+      </c>
+      <c r="D19">
+        <v>250.47</v>
+      </c>
+      <c r="E19">
+        <v>2.43</v>
+      </c>
+      <c r="F19">
+        <v>0.9644056510961163</v>
+      </c>
+      <c r="G19">
+        <v>2.34</v>
+      </c>
+      <c r="H19">
+        <v>0.2778468192644071</v>
+      </c>
+      <c r="I19">
+        <v>240.8060028076172</v>
+      </c>
+      <c r="J19">
+        <v>229.4925010681152</v>
+      </c>
+      <c r="K19">
+        <v>229.7529998779297</v>
+      </c>
+      <c r="L19">
+        <v>184.2673499298096</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>1.05</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>90.86</v>
+      </c>
+      <c r="Y19">
+        <v>253.1</v>
+      </c>
+      <c r="Z19">
+        <v>19.78</v>
+      </c>
+      <c r="AA19">
+        <v>19.49</v>
+      </c>
+      <c r="AB19">
+        <v>22.57</v>
+      </c>
+      <c r="AC19">
+        <v>294.57</v>
+      </c>
+      <c r="AD19">
+        <v>7.01</v>
+      </c>
+      <c r="AE19">
+        <v>327.06</v>
+      </c>
+      <c r="AF19">
+        <v>7.59</v>
+      </c>
+      <c r="AG19">
+        <v>-14.13</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK19">
+        <v>43.71578393235713</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>90.50505050505051</v>
+      </c>
+      <c r="C20">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>47.78</v>
+      </c>
+      <c r="E20">
+        <v>1.49</v>
+      </c>
+      <c r="F20">
+        <v>-0.8117868216084123</v>
+      </c>
+      <c r="G20">
+        <v>1.52</v>
+      </c>
+      <c r="H20">
+        <v>-1.077689607901991</v>
+      </c>
+      <c r="I20">
+        <v>47.61399917602539</v>
+      </c>
+      <c r="J20">
+        <v>45.72399978637695</v>
+      </c>
+      <c r="K20">
+        <v>43.05979988098144</v>
+      </c>
+      <c r="L20">
+        <v>39.65495003700256</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>1.11</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>23.24</v>
+      </c>
+      <c r="Y20">
+        <v>48.43</v>
+      </c>
+      <c r="Z20">
+        <v>360.52</v>
+      </c>
+      <c r="AA20">
+        <v>20.07</v>
+      </c>
+      <c r="AB20">
+        <v>28.24</v>
+      </c>
+      <c r="AC20">
+        <v>45.76</v>
+      </c>
+      <c r="AD20">
+        <v>3.09</v>
+      </c>
+      <c r="AE20">
+        <v>-17.31</v>
+      </c>
+      <c r="AF20">
+        <v>19.54</v>
+      </c>
+      <c r="AG20">
+        <v>47.46</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK20">
+        <v>34.70399548675954</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21">
+        <v>95.95959595959596</v>
+      </c>
+      <c r="C21">
+        <v>85</v>
+      </c>
+      <c r="D21">
+        <v>136.65</v>
+      </c>
+      <c r="E21">
+        <v>1.66</v>
+      </c>
+      <c r="F21">
+        <v>-0.4905605233533382</v>
+      </c>
+      <c r="G21">
+        <v>1.97</v>
+      </c>
+      <c r="H21">
+        <v>-0.3337976661643335</v>
+      </c>
+      <c r="I21">
+        <v>134.5179992675781</v>
+      </c>
+      <c r="J21">
+        <v>131.1869998931885</v>
+      </c>
+      <c r="K21">
+        <v>133.8368006896973</v>
+      </c>
+      <c r="L21">
+        <v>128.8185500717163</v>
+      </c>
+      <c r="M21">
+        <v>1.03</v>
+      </c>
+      <c r="N21">
+        <v>1.01</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>58.26</v>
+      </c>
+      <c r="Y21">
+        <v>146</v>
+      </c>
+      <c r="Z21">
+        <v>128.46</v>
+      </c>
+      <c r="AA21">
+        <v>34.32</v>
+      </c>
+      <c r="AB21">
+        <v>23.35</v>
+      </c>
+      <c r="AC21">
+        <v>52.42</v>
+      </c>
+      <c r="AD21">
+        <v>14.23</v>
+      </c>
+      <c r="AE21">
+        <v>30.34</v>
+      </c>
+      <c r="AF21">
+        <v>17.89</v>
+      </c>
+      <c r="AG21">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK21">
+        <v>33.88502885626713</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>91.91919191919192</v>
+      </c>
+      <c r="C22">
+        <v>244</v>
+      </c>
+      <c r="D22">
+        <v>63.62</v>
+      </c>
+      <c r="E22">
+        <v>1.14</v>
+      </c>
+      <c r="F22">
+        <v>-1.473135082721801</v>
+      </c>
+      <c r="G22">
+        <v>1.71</v>
+      </c>
+      <c r="H22">
+        <v>-0.7636018991683134</v>
+      </c>
+      <c r="I22">
+        <v>65.20999984741211</v>
+      </c>
+      <c r="J22">
+        <v>63.55900020599366</v>
+      </c>
+      <c r="K22">
+        <v>58.0528002166748</v>
+      </c>
+      <c r="L22">
+        <v>52.63965000152588</v>
+      </c>
+      <c r="M22">
+        <v>1.03</v>
+      </c>
+      <c r="N22">
+        <v>1.12</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>3.888888888888888</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>26.76</v>
+      </c>
+      <c r="Y22">
+        <v>66.78</v>
+      </c>
+      <c r="Z22">
+        <v>24.87</v>
+      </c>
+      <c r="AA22">
+        <v>19.66</v>
+      </c>
+      <c r="AB22">
+        <v>40</v>
+      </c>
+      <c r="AC22">
+        <v>10</v>
+      </c>
+      <c r="AD22">
+        <v>5.79</v>
+      </c>
+      <c r="AE22">
+        <v>-11.49</v>
+      </c>
+      <c r="AF22">
+        <v>17.57</v>
+      </c>
+      <c r="AG22">
+        <v>5.71</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK22">
+        <v>33.39806520277583</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23">
+        <v>96.16161616161617</v>
+      </c>
+      <c r="C23">
+        <v>418</v>
+      </c>
+      <c r="D23">
+        <v>498.56</v>
+      </c>
+      <c r="E23">
+        <v>2.1</v>
+      </c>
+      <c r="F23">
+        <v>0.3408487191892073</v>
+      </c>
+      <c r="G23">
+        <v>2.19</v>
+      </c>
+      <c r="H23">
+        <v>0.029882838685188</v>
+      </c>
+      <c r="I23">
+        <v>486.7579956054688</v>
+      </c>
+      <c r="J23">
+        <v>446.8559982299805</v>
+      </c>
+      <c r="K23">
+        <v>438.973798828125</v>
+      </c>
+      <c r="L23">
+        <v>368.1879990386963</v>
+      </c>
+      <c r="M23">
+        <v>1.09</v>
+      </c>
+      <c r="N23">
+        <v>1.11</v>
+      </c>
+      <c r="P23">
+        <v>4</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>202.56</v>
+      </c>
+      <c r="Y23">
+        <v>510.53</v>
+      </c>
+      <c r="Z23">
+        <v>26.61</v>
+      </c>
+      <c r="AA23">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="AB23">
+        <v>40.71</v>
+      </c>
+      <c r="AC23">
+        <v>10.75</v>
+      </c>
+      <c r="AD23">
+        <v>7.72</v>
+      </c>
+      <c r="AE23">
+        <v>-13.81</v>
+      </c>
+      <c r="AF23">
+        <v>18.32</v>
+      </c>
+      <c r="AG23">
+        <v>8.6</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK23">
+        <v>32.79662915500542</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>90.30303030303031</v>
+      </c>
+      <c r="C24">
+        <v>312</v>
+      </c>
+      <c r="D24">
+        <v>104.08</v>
+      </c>
+      <c r="E24">
+        <v>1.28</v>
+      </c>
+      <c r="F24">
+        <v>-1.208595778276445</v>
+      </c>
+      <c r="G24">
+        <v>1.18</v>
+      </c>
+      <c r="H24">
+        <v>-1.639741297214888</v>
+      </c>
+      <c r="I24">
+        <v>104.4179992675781</v>
+      </c>
+      <c r="J24">
+        <v>101.1429996490479</v>
+      </c>
+      <c r="K24">
+        <v>98.29580017089843</v>
+      </c>
+      <c r="L24">
+        <v>86.04310001373291</v>
+      </c>
+      <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="N24">
+        <v>1.06</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>48.73</v>
+      </c>
+      <c r="Y24">
+        <v>106.06</v>
+      </c>
+      <c r="Z24">
+        <v>33.14</v>
+      </c>
+      <c r="AA24">
+        <v>17.34</v>
+      </c>
+      <c r="AB24">
+        <v>5.07</v>
+      </c>
+      <c r="AC24">
+        <v>38.3</v>
+      </c>
+      <c r="AD24">
+        <v>5.46</v>
+      </c>
+      <c r="AE24">
+        <v>-1.52</v>
+      </c>
+      <c r="AF24">
+        <v>67.09</v>
+      </c>
+      <c r="AG24">
+        <v>-15.96</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK24">
+        <v>18.1700462343853</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>92.32323232323232</v>
+      </c>
+      <c r="C25">
+        <v>484</v>
+      </c>
+      <c r="D25">
+        <v>673.24</v>
+      </c>
+      <c r="E25">
+        <v>1.49</v>
+      </c>
+      <c r="F25">
+        <v>-0.8117868216084123</v>
+      </c>
+      <c r="G25">
+        <v>1.59</v>
+      </c>
+      <c r="H25">
+        <v>-0.9619730836316887</v>
+      </c>
+      <c r="I25">
+        <v>660.3760009765625</v>
+      </c>
+      <c r="J25">
+        <v>618.9379974365235</v>
+      </c>
+      <c r="K25">
+        <v>618.2931994628906</v>
+      </c>
+      <c r="L25">
+        <v>497.0392495727539</v>
+      </c>
+      <c r="M25">
+        <v>1.07</v>
+      </c>
+      <c r="N25">
+        <v>1.07</v>
+      </c>
+      <c r="O25" t="s">
+        <v>64</v>
+      </c>
+      <c r="P25">
+        <v>4</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>305.83</v>
+      </c>
+      <c r="Y25">
+        <v>674.8099999999999</v>
+      </c>
+      <c r="Z25">
+        <v>30.15</v>
+      </c>
+      <c r="AA25">
+        <v>22.69</v>
+      </c>
+      <c r="AB25">
+        <v>2.31</v>
+      </c>
+      <c r="AC25">
+        <v>26.87</v>
+      </c>
+      <c r="AD25">
+        <v>5.18</v>
+      </c>
+      <c r="AE25">
+        <v>4.64</v>
+      </c>
+      <c r="AF25">
+        <v>27.63</v>
+      </c>
+      <c r="AG25">
+        <v>-5</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK25">
+        <v>11.35714711133486</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26">
+        <v>92.52525252525253</v>
+      </c>
+      <c r="C26">
+        <v>80</v>
+      </c>
+      <c r="D26">
+        <v>102.78</v>
+      </c>
+      <c r="E26">
+        <v>1.34</v>
+      </c>
+      <c r="F26">
+        <v>-1.095221790657007</v>
+      </c>
+      <c r="G26">
         <v>1.43</v>
       </c>
-      <c r="F16">
-        <v>-0.7565321447252809</v>
-      </c>
-      <c r="G16">
-        <v>2.11</v>
-      </c>
-      <c r="H16">
-        <v>-0.67712079285931</v>
-      </c>
-      <c r="I16">
-        <v>28.90799980163574</v>
-      </c>
-      <c r="J16">
-        <v>28.77639999389648</v>
-      </c>
-      <c r="K16">
-        <v>27.62868000030518</v>
-      </c>
-      <c r="L16">
-        <v>26.10089998245239</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1.05</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="b">
-        <v>1</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>12.78</v>
-      </c>
-      <c r="Y16">
-        <v>31.41</v>
-      </c>
-      <c r="Z16">
-        <v>3.38</v>
-      </c>
-      <c r="AA16">
-        <v>8.77</v>
-      </c>
-      <c r="AB16">
-        <v>11.88</v>
-      </c>
-      <c r="AC16">
-        <v>34.43</v>
-      </c>
-      <c r="AD16">
-        <v>10.16</v>
-      </c>
-      <c r="AE16">
-        <v>-43.84</v>
-      </c>
-      <c r="AF16">
-        <v>305.56</v>
-      </c>
-      <c r="AG16">
-        <v>-40.98</v>
-      </c>
-      <c r="AH16" t="s">
+      <c r="H26">
+        <v>-1.226467996249523</v>
+      </c>
+      <c r="I26">
+        <v>102.5060012817383</v>
+      </c>
+      <c r="J26">
+        <v>100.475500869751</v>
+      </c>
+      <c r="K26">
+        <v>101.7346005249023</v>
+      </c>
+      <c r="L26">
+        <v>89.30530010223389</v>
+      </c>
+      <c r="M26">
+        <v>1.02</v>
+      </c>
+      <c r="N26">
+        <v>1.01</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>47.01</v>
+      </c>
+      <c r="Y26">
+        <v>105.95</v>
+      </c>
+      <c r="Z26">
+        <v>176.33</v>
+      </c>
+      <c r="AA26">
+        <v>13.89</v>
+      </c>
+      <c r="AB26">
+        <v>1.27</v>
+      </c>
+      <c r="AC26">
+        <v>7.49</v>
+      </c>
+      <c r="AD26">
+        <v>3.75</v>
+      </c>
+      <c r="AE26">
+        <v>6.91</v>
+      </c>
+      <c r="AF26">
+        <v>-15.32</v>
+      </c>
+      <c r="AG26">
+        <v>18.72</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="A27" t="s">
         <v>62</v>
       </c>
-      <c r="AI16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK16">
-        <v>22.1929540394902</v>
+      <c r="B27">
+        <v>98.98989898989899</v>
+      </c>
+      <c r="C27">
+        <v>53</v>
+      </c>
+      <c r="D27">
+        <v>26.21</v>
+      </c>
+      <c r="E27">
+        <v>2.7</v>
+      </c>
+      <c r="F27">
+        <v>1.474588595383587</v>
+      </c>
+      <c r="G27">
+        <v>3.61</v>
+      </c>
+      <c r="H27">
+        <v>2.377275188168463</v>
+      </c>
+      <c r="I27">
+        <v>27.31199951171875</v>
+      </c>
+      <c r="J27">
+        <v>25.61899995803833</v>
+      </c>
+      <c r="K27">
+        <v>22.05100006103516</v>
+      </c>
+      <c r="L27">
+        <v>20.0636999464035</v>
+      </c>
+      <c r="M27">
+        <v>1.07</v>
+      </c>
+      <c r="N27">
+        <v>1.24</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>7.96</v>
+      </c>
+      <c r="Y27">
+        <v>28.78</v>
+      </c>
+      <c r="Z27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA27">
+        <v>-0.15</v>
+      </c>
+      <c r="AB27">
+        <v>108.8</v>
+      </c>
+      <c r="AC27">
+        <v>8400</v>
+      </c>
+      <c r="AD27">
+        <v>536.84</v>
+      </c>
+      <c r="AE27">
+        <v>-18.63</v>
+      </c>
+      <c r="AF27">
+        <v>3300</v>
+      </c>
+      <c r="AG27">
+        <v>400</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK27">
+        <v>76.38220315648307</v>
       </c>
     </row>
   </sheetData>
